--- a/Los_Angeles_Clippers_2025-26_stats.xlsx
+++ b/Los_Angeles_Clippers_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1224,6 +1224,69 @@
       </c>
       <c r="S12" t="n">
         <v>18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>41</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I13" t="n">
+        <v>9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>21</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>8</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2028,6 +2091,69 @@
       </c>
       <c r="S12" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2041,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2832,6 +2958,69 @@
       </c>
       <c r="S12" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>14</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2845,7 +3034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3635,6 +3824,69 @@
         <v>2</v>
       </c>
       <c r="S12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3667,41 +3919,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.33333333333333</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.4</v>
+        <v>24.33333333333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jordan Miller</t>
+          <t>Ivica Zubac</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>16.16666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ivica Zubac</t>
+          <t>Jordan Miller</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.18181818181818</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -3711,7 +3963,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.90909090909091</v>
+        <v>11.58333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -3721,47 +3973,47 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.54545454545454</v>
+        <v>10.91666666666667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bradley Beal</t>
+          <t>Bogdan Bogdanović</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.166666666666666</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>Bradley Beal</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.454545454545454</v>
+        <v>8.166666666666666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bogdan Bogdanović</t>
+          <t>Kris Dunn</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.2</v>
+        <v>7.333333333333333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7.181818181818182</v>
+        <v>6.833333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -3791,7 +4043,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.666666666666667</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="15">
@@ -3801,7 +4053,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.181818181818182</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="16">
@@ -3867,7 +4119,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.9</v>
+        <v>9.090909090909092</v>
       </c>
     </row>
     <row r="3">
@@ -3897,7 +4149,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2</v>
+        <v>3.166666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -3907,7 +4159,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.272727272727273</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="7">
@@ -3917,7 +4169,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.909090909090909</v>
+        <v>2.166666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -3937,7 +4189,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.333333333333333</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="10">
@@ -3947,7 +4199,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.272727272727273</v>
+        <v>1.166666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -3963,7 +4215,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jordan Miller</t>
+          <t>Kobe Brown</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -3973,31 +4225,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kobe Brown</t>
+          <t>Nicolas Batum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nicolas Batum</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>John Collins</t>
+          <t>Jordan Miller</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
@@ -4007,7 +4259,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4166666666666667</v>
       </c>
     </row>
     <row r="17">
@@ -4063,27 +4315,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.45454545454546</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.666666666666667</v>
+        <v>6.272727272727272</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5</v>
+        <v>5.666666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -4093,27 +4345,27 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>4.833333333333333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jordan Miller</t>
+          <t>Bogdan Bogdanović</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3.166666666666667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bogdan Bogdanović</t>
+          <t>Jordan Miller</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4123,27 +4375,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.636363636363636</v>
+        <v>2.583333333333333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Derrick Jones Jr.</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.454545454545455</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Derrick Jones Jr.</t>
+          <t>Kris Dunn</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.363636363636364</v>
+        <v>2.416666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -4153,7 +4405,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.272727272727273</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -4209,17 +4461,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jahmyl Telfort</t>
+          <t>Kobe Sanders</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kobe Sanders</t>
+          <t>Jahmyl Telfort</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -4255,21 +4507,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jordan Miller</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>3.636363636363636</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Jordan Miller</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -4285,21 +4537,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>Bogdan Bogdanović</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.545454545454545</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bogdan Bogdanović</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.4</v>
+        <v>1.416666666666667</v>
       </c>
     </row>
     <row r="7">
@@ -4309,7 +4561,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.363636363636364</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="8">
@@ -4325,7 +4577,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kobe Sanders</t>
+          <t>Nicolas Batum</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -4339,37 +4591,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0.9166666666666666</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nicolas Batum</t>
+          <t>Cam Christie</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cam Christie</t>
+          <t>Kris Dunn</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.875</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Kobe Sanders</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="14">
@@ -4433,7 +4685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4694,6 +4946,27 @@
         <v>246</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>133</v>
+      </c>
+      <c r="D13" t="n">
+        <v>127</v>
+      </c>
+      <c r="E13" t="n">
+        <v>260</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
